--- a/dataset/3_tax_and_charges_rules/structured/Sources_of_every_rule.xlsx
+++ b/dataset/3_tax_and_charges_rules/structured/Sources_of_every_rule.xlsx
@@ -15,16 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,35 +47,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -383,27 +357,27 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>retrieved</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>supports</t>
         </is>
@@ -415,6 +389,16 @@
           <t>S0</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>No source found</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>`assumed` rows only</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -422,6 +406,26 @@
           <t>S1</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fyers, Charges list (current schedule)</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>https://fyers.in/charges-list</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>current brokerage, DP fee split (Rs 3.5 CDSL + Rs 9 Fyers), AMC, account opening, statutory rates as Fyers lists them</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -429,6 +433,26 @@
           <t>S2</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fyers, Pricing page and its markdown mirror</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>https://fyers.in/pricing ; https://fyers.in/pricing.md</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>current Standard plan brokerage (delivery/ETF Rs 20 or 0.3%; futures Rs 20 or 0.03%), Prime plan Rs 15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -436,6 +460,26 @@
           <t>S3</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fyers, Online Pricing page, Wayback copies of 2015-11-15 and 2016-03-16</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20151115003240/http://fyers.in:80/fyers-online-pricing/ ; https://web.archive.org/web/20160316230009/https://fyers.in/fyers-online-pricing/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>delivery 0.1% and futures 0.01% of turnover on each leg; earliest archived Fyers price page; NSE member 90061, SEBI INZ000008524</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -443,6 +487,26 @@
           <t>S4</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fyers, Online Pricing page, Wayback copy of 2016-04-13</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20160413044637/http://fyers.in:80/fyers-online-pricing/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>delivery 0.1% or Rs 100 per order; futures 0.01% or Rs 100 per order</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -450,6 +514,26 @@
           <t>S5</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fyers, Pricing page, Wayback copy of 2017-08-08</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20170808163252/https://www.fyers.in/pricing/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>delivery Rs 20 per executed order or 0.1%; futures Rs 20 or 0.01%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -457,6 +541,26 @@
           <t>S6</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fyers notice: Free Investment Zone, zero brokerage for equity delivery, effective 2018-02-06 (Wayback copy of 2018-09-15)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20180915id_/https://fyers.in/free-investment-zone-zero-brokerage-equity-delivery/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>delivery brokerage zero from 2018-02-06; CEO reply: Fyers started in 2015</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -464,6 +568,26 @@
           <t>S7</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fyers, Pricing page, Wayback copy of 2018-09-15</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20180915154942/https://fyers.in/pricing/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>demat debit Rs 20 plus depository charges at actuals; demat AMC Rs 400 plus tax (levied by IL&amp;FS, ISSL); delivery free</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +595,26 @@
           <t>S8</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fyers, Charges list of 2019-11-15 and Pricing page of 2019-11-19 (Wayback)</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20191115212554/https://fyers.in/charges-list/ ; https://web.archive.org/web/20191119235506/https://fyers.in/pricing/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fyers-own demat: debit Rs 10 + Rs 5.5 CDSL; AMC Rs 0 / FREE; futures Rs 20 or 0.01%</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -478,6 +622,26 @@
           <t>S9</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fyers notice: Updates during the lockdown, dated 07/05/2020 (Wayback copy of 2020-05-12)</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20200512id_/https://fyers.in/notice-board/updates-during-the-lockdown/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>futures brokerage Rs 20 or 0.03% (was 0.01%) with effect from 2020-05-11</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -485,6 +649,26 @@
           <t>S10</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fyers support article: Does FYERS levy Annual Maintenance Charges (AMC)? (Wayback copies of 2020-11-24 and 2021-01-27)</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20201124100029/https://fyers.in/support/article/does-fyers-levy-annual-maintenance-charges-amc/ ; https://web.archive.org/web/20210127142319/https://fyers.in/support/article/does-fyers-levy-annual-maintenance-charges-amc/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>demat AMC Rs 300 + GST a year from 2020-04-01; accounts opened on or before 2020-03-31 keep zero AMC; Rs 225 in the first year for accounts opened from 2020-12-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -492,6 +676,26 @@
           <t>S11</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fyers support article: What are the account opening charges at FYERS? (Wayback copies of 2020-01-02, 2020-08-09, 2021-01-27) and notice Removal of Account Opening Charges (2021-01-18)</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20200102034822/https://fyers.in/support/article/what-are-the-account-opening-charges-at-fyers/ ; https://web.archive.org/web/20200809105456/https://fyers.in/support/article/what-are-the-account-opening-charges-at-fyers/ ; https://web.archive.org/web/20210127125221/https://fyers.in/support/article/what-are-the-account-opening-charges-at-fyers/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no account-opening charge (Jan 2020); Rs 400 + GST from 2020-04-01; nil from 2020-11-24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -499,6 +703,26 @@
           <t>S12</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fyers, Pricing page, Wayback copies of 2021-07-25, 2021-08-13 and 2021-09-10</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20210725004635/https://fyers.in/pricing/ ; https://web.archive.org/web/20210813104221/https://fyers.in/pricing/ ; https://web.archive.org/web/20210910105727/https://fyers.in/pricing/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021-07-25: debit Rs 10 + 5.5, AMC free (limited offer); 2021-08-13: debit Rs 7 + 5.5; 2021-09-10: AMC FREE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -506,6 +730,26 @@
           <t>S13</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fyers, Charges list, Wayback copy of 2024-07-19</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20240719032630/https://fyers.in/charges-list/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>demat debit Rs 7 + Rs 5.5 (CDSL); AMC Rs 0; futures Rs 20 or 0.03%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -513,6 +757,26 @@
           <t>S14</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fyers notice: Revision of Brokerage, MTF Interest, and Other Charges Effective October 1, 2024, dated 30 Sep 2024 (Wayback copy of 2024-12-04)</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20241204id_/https://fyers.in/notice-board/revision-of-brokerage-mtf-interest-and-other-charges-effective-october-1-2024/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>delivery 0.3% or Rs 20 from 2024-10-01; DP Rs 12.5 to Rs 3.5 per transaction; intraday/F&amp;O unchanged; NSE charges and STT changes from 2024-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -520,6 +784,26 @@
           <t>S15</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fyers notice: Simplified and Cost-Efficient: New DP Charges from 2nd June 2025 (Wayback copy of 2025-08-14)</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20250814id_/https://fyers.in/notice-board/simplified-and-cost-efficient-new-dp-charges-from-2nd-june-2025/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>flat Rs 12.5 + GST per ISIN per day from 2025-06-02 (Rs 3.5 CDSL + Rs 9 Fyers per S1)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -527,6 +811,26 @@
           <t>S16</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fyers notices: Free AMC Offer Extended Indefinitely (2021-09-25) and AMC waived off for the existing clients w.e.f. 1st October 2021 (Wayback copies)</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20210925id_/https://fyers.in/notice-board/free-amc-offer-extended-indefinitely/ ; https://web.archive.org/web/20210930id_/https://fyers.in/notice-board/amc-waived-off-for-the-existing-clients-w-e-f-1st-october-2021/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AMC waived for existing clients from 2021-10-01; free AMC for new clients extended indefinitely</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -534,6 +838,26 @@
           <t>S17</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fyers support article: What are the DP charges levied by FYERS? (Wayback copy of 2020-08-10)</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20200810id_/https://fyers.in/support/article/what-are-the-dp-charges-levied-by-fyers/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rs 10 + Rs 5.5 (CDSL charges) on the sell side</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -541,6 +865,26 @@
           <t>S18</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Finance Bill 2012, Memorandum explaining the provisions (Ministry of Finance), page 13, clause 153</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2012-2013/ub2012-13/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>STT on delivery-based purchase and sale of equity shares and units of an equity oriented fund: existing 0.125%, proposed 0.1% from 2012-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -548,6 +892,26 @@
           <t>S19</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Finance Bill 2013 memorandum (Ministry of Finance) and CBDT Circular 03/2014, Explanatory Notes to the Finance Act 2013, para 49 (copy of the circular)</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2013-2014/ub2013-14/mem/mem1.pdf ; https://itgoawbunit.org/pdf/233247133cbdt-releases-explanatory-notes-on-finance-act-2013.pdf</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>STT from 2013-06-01: units of equity oriented fund purchase 0.1% to nil, sale 0.1% to 0.001%; futures 0.017% to 0.01%; sale of a unit to the mutual fund 0.25% to 0.001%; rates for 2013-14 unchanged from 2012-13 (nil to Rs 2 lakh, 10% to Rs 5 lakh, 20% to Rs 10 lakh, 30% above); rebate of Rs 2,000 (or the tax if less) for resident individuals with total income up to Rs 5 lakh from AY 2014-15; surcharge 10% above Rs 1 crore; cess 2% plus 1%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -555,6 +919,26 @@
           <t>S20</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FATAX/32385 dated 2016-05-16, Changes in relation to rates of STT</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FATAX32385.pdf</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>STT table from 2016-06-01: sale of a unit of an equity oriented fund 0.001% (no change); futures 0.01% (no change); options 0.017% to 0.05%</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -562,6 +946,26 @@
           <t>S21</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FATAX/56235 dated 2023-04-01, Changes in relation to rates of STT</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>https://archives.nseindia.com/content/circulars/FATAX56235.pdf</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Finance Act 2023: sale of a futures in securities 0.0125% from 2023-04-01 (up to 2023-03-31: 0.01%)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -569,6 +973,26 @@
           <t>S22</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FATAX/63809 dated 2024-09-09, Changes in relation to rates of STT</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FATAX63809.pdf</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Finance Act 2024: sale of a futures in securities 0.02% from 2024-10-01 (up to 2024-09-30: 0.0125%)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -576,6 +1000,26 @@
           <t>S23</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FATAX/73524 dated 2026-03-31, Changes in relation to rates of STT (full table)</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FATAX73524.pdf ; https://www.nseindia.com/static/products-services/equity-derivatives-securities-transaction-tax</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Finance Act 2026: futures 0.05% from 2026-04-01 (up to 2026-03-31: 0.02%); unit of an equity oriented fund 0.001% seller (no change); no item for other units</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -583,6 +1027,26 @@
           <t>S24</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Securities Transaction Tax Rules, 2004, rule 4 (rounding off)</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/35003869/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>STT is rounded to the nearest rupee, 50 paise or more rounding up</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -590,6 +1054,26 @@
           <t>S25</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FA/46730 dated 2020-12-18, Revision in Transaction Charges</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FA46730.pdf</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>cash market Rs 3.25 to 3.45 per lakh each side, equity futures Rs 1.90 to 2.00 (first slab), applicable from 2021-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -597,6 +1081,26 @@
           <t>S26</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FA/56129 dated 2023-03-24, Revision in Transaction Charges</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>https://archives.nseindia.com/content/circulars/FA56129.pdf</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>from 2023-04-01: cash Rs 3.25, futures Rs 1.90 per lakh (first slab); IPFT contribution Rs 0.01 to Rs 10 per crore</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -604,6 +1108,26 @@
           <t>S27</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FA/61137 dated 2024-03-14, Revision in Transaction Charges</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FA61137.pdf</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>from 2024-04-01: cash Rs 3.22, futures Rs 1.88 per lakh (first slab)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -611,6 +1135,26 @@
           <t>S28</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FA/64232 dated 2024-09-27, Revision in Transaction Charges (SEBI true to label)</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FA64232.pdf</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>uniform from 2024-10-01: cash Rs 2.97, equity futures Rs 1.73 per lakh each side</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -618,6 +1162,26 @@
           <t>S29</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NSE circular NSE/FA/73061 dated 2026-02-27, Revision in Transaction Charges</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/content/circulars/FA73061.pdf</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>from 2026-03-01: cash Rs 306.99, futures Rs 182.99 per crore each side; IPFT contribution Rs 0.01 per crore</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -625,6 +1189,26 @@
           <t>S30</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fyers support articles: statutory charges (Wayback 2020-08-10), SEBI turnover fees (2020-11-01), GST on total charges (2020-11-04)</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20200810id_/https://fyers.in/support/article/what-are-the-statutory-charges-levied-by-the-government-and-regulatory-authorities-2/ ; https://web.archive.org/web/20201104id_/https://fyers.in/support/article/how-is-gst-calculated-on-the-total-charges/</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Fyers' own schedule in 2020: STT delivery 0.1% both sides, futures 0.01% sell; NSE transaction 0.00325% cash, futures 0.0019% + clearing 0.0005%; SEBI Rs 10 per crore; GST 18% on brokerage + transaction charges (exchange + clearing)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -632,6 +1216,26 @@
           <t>S31</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fyers brokerage and margin calculator scripts, Wayback copies of 2018-03-04, 2019-06-09 and 2020-05-22</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20180304id_/https://fyers.in/wp-content/plugins/domy-brokerage-margin-calculator/assets/js/brokerage_margin_calculator.js ; https://web.archive.org/web/20190609id_/https://fyers.in/wp-content/plugins/domy-brokerage-margin-calculator/assets/js/brokerage_margin_calculator.js?1_2&amp;ver=4 ; https://web.archive.org/web/20200522id_/https://fyers.in/wp-content/plugins/domy-brokerage-margin-calculator/assets/js/brokerage_margin_calculator.js?1_3&amp;ver=4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fyers' own constants: cash transaction 0.00325%, futures 0.0024% (0.0019% + 0.0005% clearing), GST 18% on brokerage + transaction charges; SEBI 0.00015% (2018, 2019) and 0.0001% (2020); state-wise stamp duty table (Maharashtra delivery 0.01%, futures 0.002%)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -639,6 +1243,26 @@
           <t>S32</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SEBI notification SEBI/LAD-NRO/GN/2019/03 of 2019-03-22 (Payment of Fees Amendment Regulations 2019, in force 2019-04-01; copy in an exchange notice) and SEBI Board memorandum of March 2019</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>https://www.cse-india.com/upload/cse_notice/REVISED_SEBI_TURNOVER_FEES.htm ; https://www.sebi.gov.in/sebi_data/meetingfiles/mar-2019/1553244864312_1.pdf</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>broker turnover fee 0.00010 per cent (Rs 10 per crore) for cash and equity derivatives from 2019-04-01; the Board memorandum says the fee then was Rs 15 per crore</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -646,6 +1270,26 @@
           <t>S33</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SEBI press release PR 24/2020 of 2020-04-27 and Board memorandum of July 2020</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>https://www.sebi.gov.in/media/press-releases/apr-2020/sebi-reduces-broker-turnover-fees-and-filing-fees-for-issuers_46571.html ; https://www.sebi.gov.in/sebi_data/meetingfiles/jul-2020/1594293677017_1.pdf</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>broker turnover fee cut to 50% for June 2020 to March 2021; existing fee Rs 10 per crore</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -653,6 +1297,26 @@
           <t>S34</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Moneylife, Sebi reduces brokers' fee by 25%, January 2017</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>https://www.moneylife.in/article/sebi-reduces-brokers-fee-by-25-percentage/49497.html</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>broker turnover fee cut from Rs 20 to Rs 15 per crore, announced after the SEBI Board meeting of January 2017; effective date not stated</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -660,6 +1324,26 @@
           <t>S35</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NSE page Stamp Duty and PIB press release of 2020-06-30 on stamp duty on securities from 1 July 2020</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/static/invest/first-time-investor-stamp-duty-charges-taxes ; https://www.pib.gov.in/PressReleasePage.aspx?PRID=1635399</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>uniform stamp duty from 2020-07-01, buyer only: delivery 0.015%, equity futures 0.002%, options 0.003%</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -667,6 +1351,26 @@
           <t>S36</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HDFC Mutual Fund FAQ on stamp duty and LIC Mutual Fund FAQ on stamp duty on mutual fund units</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>https://files.hdfcfund.com/s3fs-public/2020-07/FAQs%20on%20Stamp%20Duty.pdf ; https://www.licmf.com/assets/pdfs/FAQs-on-Stamp-Duty-on-Mutual-Fund-Units.pdf</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>stamp duty of 0.005% on the issue (purchase) of mutual fund units from 2020-07-01; none before</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -674,6 +1378,26 @@
           <t>S37</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Service tax rate history: Wikipedia, Service tax; Taxguru on Krishi Kalyan Cess; CBEC notifications 21/2015-ST and 28/2016-ST</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Service_tax ; https://taxguru.in/service-tax/krishi-kalyan-cess-applicability-open-issues.html</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10.30% from 2009-02-24; 12.36% from 2012-04-01; 14% from 2015-06-01; 14.5% from 2015-11-15; 15% from 2016-06-01 to 2017-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -681,6 +1405,26 @@
           <t>S38</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CDSL media release of 2024-09-26: uniform transaction tariff</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>https://www.cdslindia.com/Downloads/About/Media/Final_26%20Sep%202024%20Media%20Release_Tariffrevised.pdf</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>uniform Rs 3.50 per debit transaction from 2024-10-01 (discount Rs 0.25 for women first holders and for mutual fund and bond ISINs)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -688,6 +1432,26 @@
           <t>S39</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fyers, Charges list, Wayback copies of 2022-01-24, 2023-06-05 and 2025-03-17</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20220124035340/https://fyers.in/charges-list ; https://web.archive.org/web/20230605110508/https://fyers.in/charges-list/ ; https://web.archive.org/web/20250317024407/https://fyers.in/charges-list/</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GST base wording: brokerage + transaction charges (2022); adds SEBI turnover fee (by 2023-06-05); adds NSE IPFT (by 2025-03-17)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -695,6 +1459,26 @@
           <t>S40</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Finance Bill 2012, Memorandum explaining the provisions (Ministry of Finance), clause 41: rate of tax for short term capital gain under section 111A</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2012-2013/ub2012-13/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>tax on short-term capital gains on STT-paid equity shares and equity oriented fund units is 15%, raised from 10% by the Finance Act 2008 with effect from 1 April 2009; rates for 2012-13: nil to Rs 2 lakh, 10% to Rs 5 lakh, 20% to Rs 10 lakh, 30% above; no surcharge on individuals; cess 2% plus 1%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -702,6 +1486,26 @@
           <t>S41</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Finance (No.2) Bill 2014, Memorandum (direct taxes): business trusts; long-term capital gains on debt oriented mutual funds; tax on long-term capital gains on units</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2014-2015/ub2014-15/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>equity shares get: long-term gains exempt, short-term gains 15% (business trust units to be treated the same); long-term gains on STT-paid equity oriented fund units are not chargeable; before the Bill a mutual fund unit was long-term after 12 months; proposed 36 months for units of funds other than equity oriented; 10% concession in section 112 for units withdrawn (proposed from AY 2015-16); rates for 2014-15: nil to Rs 2.5 lakh, 10% to Rs 5 lakh, 20% to Rs 10 lakh, 30% above; surcharge 10% above Rs 1 crore</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -709,6 +1513,26 @@
           <t>S42</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CBDT Circular No. 01/2015 of 2015-01-21, Explanatory Notes to the provisions of the Finance (No.2) Act 2014, paras 5.2 and 30.2 (copy of the circular)</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>https://support.taxmann.com/pdf/circular/circular1_2015.pdf</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>units of a mutual fund other than equity oriented: short-term if held 36 months or less, but 12 months for transfers from 2014-04-01 to 2014-07-10; the 10% option (tax at most 10% of the gain without indexation) stays for such units only for transfers from 2014-04-01 to 2014-07-10</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -716,6 +1540,26 @@
           <t>S43</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Finance Bill 2018, Memorandum explaining the provisions (Ministry of Finance): withdrawal of section 10(38) and new section 112A</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2018-2019/ub2018-19/memo/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>long-term gains on STT-paid equity shares and equity oriented fund units were exempt under section 10(38) until withdrawn; from the year starting 2018-04-01 taxed at 10% on gains above Rs 1 lakh under section 112A, no indexation; cost of assets acquired before 1 Feb 2018 is the higher of actual cost and the lower of the value on 31 Jan 2018 and the sale value; value on 31 Jan 2018 is the highest quoted price (listed) or the NAV (unlisted units); 2018-19 slabs unchanged (nil to Rs 2.5 lakh, 5% to Rs 5 lakh, 20% to Rs 10 lakh, 30% above); surcharge 10% (Rs 50 lakh to Rs 1 crore) and 15% above; a Health and Education Cess of 4% replaces the cess of 2% plus 1%</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -723,6 +1567,26 @@
           <t>S44</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Finance Bill 2017, Memorandum explaining the provisions (Ministry of Finance): shifting the base year for indexation from 1981 to 2001; rationalization of taxation of dividend; advance tax on dividend</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2017-2018/ub2017-18/memo/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>cost inflation index base year moves to 2001-02 from AY 2018-19 (transfers from 2017-04-01); Finance Act 2016 introduced section 115BBDA from 2017-04-01 (AY 2017-18): 10% on dividends above Rs 10 lakh from domestic companies for resident individuals, HUFs and firms; 2017-18: 5% band for Rs 2.5 to 5 lakh (was 10%); section 87A rebate cut from Rs 5,000 to Rs 2,500 and limited to income up to Rs 3.5 lakh; surcharge 10% (Rs 50 lakh to Rs 1 crore) and 15% above; cess 2% plus 1%</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -730,6 +1594,26 @@
           <t>S45</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Finance Bill 2020, Memorandum explaining the provisions (Ministry of Finance): abolition of dividend distribution tax</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2020-21/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>dividends and mutual fund unit income taxable in the holder's hands at applicable rates for income received on or after 2020-04-01; before that section 10(34) and 10(35) exempted them because the payer paid distribution tax; section 115BBDA limited to dividends up to 2020-03-31; 2020-21: new optional section 115BAC slabs (nil to Rs 2.5 lakh, 5%, 10%, 15%, 20%, 25% up to Rs 15 lakh, 30% above); surcharge tiers 10%, 15%, 25% and 37% where the 25% and 37% tiers look at income excluding section 111A and 112A gains and the surcharge on those gains is capped at 15%</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -737,6 +1621,26 @@
           <t>S46</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Finance (No.2) Bill 2024 (Bill No. 55 of 2024), text: clause 3 (section 2(42A)), clause 21 (section 50AA), clause 31 (section 112A), First Schedule</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2024-25/doc/Finance_Bill.pdf</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>from 2024-07-23: holding period 24 months, 12 months for listed securities including units, units of equity oriented funds; section 111A 15% before and 20% on or after 2024-07-23; section 112A 10% before and 12.5% on or after, limit Rs 1.25 lakh on the aggregate; section 112 12.5%; section 50AA covers a unit of a Specified Mutual Fund acquired on or after 2023-04-01; new Specified Mutual Fund definition from 2026-04-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -744,6 +1648,26 @@
           <t>S47</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Finance Bill 2024, Memorandum explaining the provisions (Ministry of Finance): rationalisation of capital gains; amendment to the definition of Specified Mutual Fund</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2024-25/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>holding periods 12 and 24 months and rates 20% and 12.5% from 2024-07-23, exemption Rs 1.25 lakh, indexation removed; Finance Act 2023 deemed gains on Specified Mutual Funds (not more than 35% in equity shares, which caught ETFs, gold mutual funds and gold ETFs) short-term whatever the holding period; new definition (more than 65% in debt and money market instruments) from AY 2026-27; new regime slabs for 2024-25 (nil to Rs 3 lakh, 5% to Rs 7 lakh, 10% to Rs 10 lakh, 15% to Rs 12 lakh, 20% to Rs 15 lakh, 30% above) and for 2023-24 (nil to Rs 3 lakh, 5% to Rs 6 lakh, 10% to Rs 9 lakh, 15% to Rs 12 lakh, 20% to Rs 15 lakh, 30% above); old slabs unchanged; surcharge 10%, 15%, 25% (new regime tops at 25%) with a 15% cap on the tax on dividend and section 111A, 112 and 112A income</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -751,6 +1675,26 @@
           <t>S48</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PIB, FAQs issued by CBDT on the new capital gains tax regime proposed in the Union Budget 2024-25, Release ID 2036604 of 2024-07-24</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2036604</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>new provisions apply to any transfer on or after 2024-07-23; holding period one year for listed securities and two years for all other assets; section 111A rate 20%, section 112A rate 12.5%, other long-term gains 12.5% without indexation; exemption limit Rs 1.25 lakh applies for FY 2024-25 and later years</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -758,6 +1702,26 @@
           <t>S49</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AMFI (Association of Mutual Funds in India), Tax Regime for Mutual Funds, applicable for FY 2024-25</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>https://www.amfiindia.com/investor/knowledge-center-info?zoneName=TaxRegimeForMutualFunds</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Gold ETFs, liquid and debt funds are Specified Mutual Funds under section 50AA for FY 2024-25 (units acquired on or after 2023-04-01: gains deemed short-term); from FY 2025-26 only debt-oriented funds; other non-equity units: long-term after 12 months (listed) or 24 months (unlisted) for transfers on or after 2024-07-23, after 36 months before</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -765,6 +1729,26 @@
           <t>S50</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cost inflation index, old series (base year 1981-82 = 100): CBDT notifications under clause (v) of the Explanation to section 48: No. 59/2010 of 2010-07-21 (2010-11: 711); No. 35/2011 of 2011-06-23 (2011-12: 785); No. 38/2012 of 2012-09-17 (2012-13: 852); No. 40/2013 of 2013-06-06 (2013-14: 939); No. 31/2014 of 2014-06-11 (2014-15: 1024); No. 60/2015 of 2015-07-24 (2015-16: 1081); No. 42/2016 of 2016-06-02 (2016-17: 1125). Copies of the notification texts</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>https://www.simpletaxindia.net/2010/07/cost-inflation-index-2010-11financial.html ; https://www.simpletaxindia.net/2011/06/cost-inflation-index-2011-12-financial.html ; https://taxguru.in/income-tax/cost-inflation-index-financial-year-201213.html ; https://taxguru.in/income-tax/cost-inflation-index-financial-year-201314-sources.html ; https://taxguru.in/income-tax/cost-inflation-index-financial-year-201415.html ; https://abcaus.in/incometax/cbdt-cost-inflation-index-fy-201516-notified-1081-uptodate-cii-table-from-1981-82.html ; https://www.taxscan.in/cbdt-notifies-1125-as-cost-inflation-index-for-financial-year-2016-17/924</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>the index for each financial year from 2010-11 to 2016-17 on the old base; for 2016-17 the copy is a news report of the notification (Rs 1125), confirmed by the TaxGuru table</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -772,6 +1756,26 @@
           <t>S51</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Income Tax Department, Notified cost inflation index under section 48 Explanation (v), new series (base year 2001-02 = 100), as per notification S.O. 3266(E) [No. 63/2019] of 2019-09-12 (copy of the department table hosted by Quicko, updated to 2020-21)</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>https://assets.learn.quicko.com/wp-content/uploads/2020/07/22120356/Income-Tax-Department-CII-Cost-Inflation-Index.pdf</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>index 2001-02 to 2020-21 on the new base (2010-11: 167 ... 2020-21: 301); used for transfers from 2017-04-01 (S44)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -779,6 +1783,26 @@
           <t>S52</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cost inflation index 2021-22 to 2025-26: TaxGuru consolidated table quoting notification 70/2025 of 2025-07-01, and ClearTax table; individual notifications No. 21/2023 of 2023-04-10 (348) and No. 44/2024 of 2024-05-24 (363) as reported by TaxIndiaUpdates</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>https://taxguru.in/income-tax/cost-inflation-index-meaning-and-index-for-all-the-years.html ; https://cleartax.in/s/cost-inflation-index ; https://taxindiaupdates.in/cost-inflation-index/</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>new-series index 2021-22: 317; 2022-23: 331; 2023-24: 348; 2024-25: 363; 2025-26: 376 (secondary: the gazette text itself was not reachable)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -786,6 +1810,26 @@
           <t>S53</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Business Standard, CBDT notifies Cost Inflation Index for FY2026-27 at 384 (2026-07-16); ClearTax, Cost Inflation Index for FY 2026-27</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/finance/news/cbdt-cost-inflation-index-fy27-384-capital-gains-tax-126071600429_1.html ; https://cleartax.in/s/cost-inflation-index</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>index 384 for 2026-27, from a gazette notification of 2026-07-15 applying from 2026-04-01 (secondary: the notification number was not stated)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -793,6 +1837,26 @@
           <t>S54</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Income-tax Act 1961, section 74(2) (Indian Kanoon copy); Income Tax Department e-Filing help, Set off/Carry forward of Losses (FAQs on the Income-tax Act 2025)</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/1129438/ ; https://www.incometax.gov.in/iec/foportal/help/all-topics/e-filing-services/set-offcarry-forward-losses</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>a capital loss is carried forward for at most eight assessment years after the year it arose; short-term losses set off against any capital gain, long-term losses against long-term gains only; losses of earlier years carry into the Income-tax Act 2025 on the old terms</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -800,6 +1864,26 @@
           <t>S55</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Income-tax Act 2025 (Act 30 of 2025), sections 196, 197 and 198 (Indian Kanoon copies); Finance Bill 2026 memorandum, surcharge paragraphs (sections 196, 197 and 198 listed in the order of 111A, 112 and 112A)</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/33926599/ ; https://indiankanoon.org/doc/190890701/ ; https://indiankanoon.org/doc/76321359/ ; https://www.indiabudget.gov.in/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>from 2026-04-01: short-term gains on STT-paid equity 20% (section 196); other long-term gains 12.5% (section 197); long-term gains on STT-paid equity 12.5% above Rs 1,25,000 (section 198); tax year 2026-27: default slabs nil to Rs 4 lakh, 5%, 10%, 15%, 20%, 25% up to Rs 24 lakh, 30% above (section 202); option slabs nil to Rs 2.5 lakh, 5%, 20%, 30%; surcharge tiers and the 15% cap as before; cess 4%</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -807,6 +1891,26 @@
           <t>S56</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Finance Bill 2010, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax for AY 2011-12</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget_archive/ub2010-11/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2010-11 individual slabs: nil to Rs 1,60,000, 10% to Rs 5 lakh, 20% to Rs 8 lakh, 30% above; no surcharge on individuals; cess 2% plus 1%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -814,6 +1918,26 @@
           <t>S57</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Finance Bill 2011, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2011-2012/ub2011-12/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2011-12 individual slabs: nil to Rs 1,80,000, 10% to Rs 5 lakh, 20% to Rs 8 lakh, 30% above; no surcharge on individuals; cess 2% plus 1% continue</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -821,6 +1945,26 @@
           <t>S58</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Finance Bill 2015, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2015-2016/ub2015-16/memo/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2015-16 slabs unchanged (nil to Rs 2.5 lakh, 10% to Rs 5 lakh, 20% to Rs 10 lakh, 30% above); surcharge 12% above Rs 1 crore</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -828,6 +1972,26 @@
           <t>S59</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Finance Bill 2016, Memorandum explaining the provisions (Ministry of Finance): rates; rebate under section 87A; rationalization of taxation of income by way of dividend</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2016-2017/ub2016-17/memo/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2016-17 slabs unchanged; surcharge 15% above Rs 1 crore; section 87A rebate raised from Rs 2,000 to Rs 5,000 for income up to Rs 5 lakh; dividends exempt in the holder's hands under section 10(34) because the company pays distribution tax; dividend above Rs 10 lakh taxed at 10% for individuals, HUFs and firms from 2017-04-01 (AY 2017-18)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -835,6 +1999,26 @@
           <t>S60</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Finance Bill 2019 (Bill No. 5 of 2019, interim budget), text, clause 8: section 87A</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget_archive/ub2019-20/fb/bill.pdf</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>section 87A income limit raised from Rs 3.5 lakh to Rs 5 lakh and rebate from Rs 2,500 to Rs 12,500 from 2020-04-01 (AY 2020-21, financial year 2019-20)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -842,6 +2026,26 @@
           <t>S61</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Finance (No.2) Bill 2019, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2019-20/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2019-20 old-regime slabs (nil to Rs 2.5 lakh, 5% to Rs 5 lakh, 20% to Rs 10 lakh, 30% above); surcharge 10% (Rs 50 lakh to Rs 1 crore), 15% (to Rs 2 crore), 25% (to Rs 5 crore), 37% above; cess 4%</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -849,6 +2053,26 @@
           <t>S62</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Finance Bill 2021, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2021-22/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2020-21 and 2021-22 rates unchanged: old slabs, section 115BAC slabs (5%, 10%, 15%, 20%, 25%, 30%), surcharge tiers with the 15% cap on dividend and section 111A and 112A tax</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -856,6 +2080,26 @@
           <t>S63</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Finance Bill 2022, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2022-23/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2022-23 rates unchanged; from 2022-23 the 15% cap on surcharge covers tax on dividend and on section 111A, 112 and 112A income (section 112 added)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -863,6 +2107,26 @@
           <t>S64</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Finance Bill 2023, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax; rebate under section 87A</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2023-24/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2022-23 section 115BAC slabs (5% to 30% in Rs 2.5 lakh steps); from 2023-24 the new regime is the default (nil to Rs 3 lakh, 5% to Rs 6 lakh, 10% to Rs 9 lakh, 15% to Rs 12 lakh, 20% to Rs 15 lakh, 30% above) with surcharge tiers 10%, 15%, 25% (top 25%); rebate of the whole tax for income up to Rs 7 lakh in the new regime, Rs 5 lakh otherwise</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -870,6 +2134,26 @@
           <t>S65</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Finance Bill 2025, Memorandum explaining the provisions (Ministry of Finance): rates of income-tax; rebate under section 87A</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2025-26/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>new-regime slabs for 2024-25 (3/7/10/12/15 lakh) and 2025-26 (nil to Rs 4 lakh, 5%, 10%, 15%, 20%, 25% up to Rs 24 lakh, 30% above); rebate up to Rs 25,000 for income up to Rs 7 lakh (2023-24, 2024-25) and Rs 60,000 for income up to Rs 12 lakh (2025-26), with marginal relief, and not against tax on income at special rates such as section 111A and 112 gains</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -877,6 +2161,26 @@
           <t>S66</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PIB, Cabinet approves Taxation Laws (Amendment) Bill, 2019 (Release ID 1592560); PRS Legislative Research, The Taxation Laws (Amendment) Ordinance, 2019</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/Pressreleaseshare.aspx?PRID=1592560&amp;reg=3&amp;lang=2 ; https://prsindia.org/billtrack/prs-products/prs-ordinance-summary-3348</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>the enhanced surcharge (25% and 37%) brought in by the Finance Act 2019 does not apply to capital gains on STT-paid listed equity shares and units (sections 111A and 112A) for 2019-20</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -884,6 +2188,26 @@
           <t>S67</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Income-tax Act 1961, section 288B (Indian Kanoon copy)</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/1566795/</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>tax payable is rounded to the nearest multiple of ten rupees (paise ignored; a last figure of five or more rounds up)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -891,6 +2215,26 @@
           <t>S68</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Income-tax Act 1961, section 112A(6) (Indian Kanoon copy); ITAT Ahmedabad, Jayshreeben Jayantibhai Palsana vs ITO, ITA 1014/Ahd/2025 of 2025-08-12, as reported by TaxTMI and CounselVise</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/73220/ ; https://www.taxtmi.com/article/detailed?id=14970 ; https://counselvise.com/blogs/itat-ahmedabad-rules-on-section-87a-rebate-against-stcg-under-section-111a-a-y-2024-25</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>the section 87A rebate is taken from the tax on total income reduced by the tax on section 112A gains; section 87A has no exclusion for section 111A gains; the tribunal allowed the new-regime rebate against tax on section 111A gains for AY 2024-25 although the department had denied it</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -898,6 +2242,26 @@
           <t>S69</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>freefincal, ITR Efiling: How the order of LTCG set-off can cost you more than you think (2025-06-15)</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>https://freefincal.com/itr-efiling-how-the-order-of-ltcg-set-off-can-cost-you-more-than-you-think/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>brought-forward long-term losses are set off against the gains before the yearly section 112A exemption is applied; unused basic exemption is usually set off against the highest-rate gain first; the Income Tax portal calculator was reported to apply it to equity gains before the section 112A exemption (blog, not law)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -905,6 +2269,26 @@
           <t>S70</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Income-tax Act 2025, section 156: rebate of income-tax (Indian Kanoon copy)</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/144285716/</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>tax year 2026-27: rebate of 100% of the tax or Rs 12,500 for total income up to Rs 5 lakh; for income taxed under section 202(1) up to Rs 60,000 for total income up to Rs 12 lakh with marginal relief, not more than the tax at the section 202(1) rates</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -912,6 +2296,26 @@
           <t>S71</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Finance Bill 2010, Memorandum explaining the provisions relating to direct taxes (Ministry of Finance)</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget_archive/ub2010-11/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>"Limit of turnover or gross receipts for the purpose of audit of accounts": the section 44AB limit for a person carrying on business goes from forty lakh to sixty lakh rupees, taking effect from 1 April 2011, assessment year 2011-12 (financial year 2010-11); the memorandum has no paragraph on the securities transaction tax, so STT rates did not change with the Finance Act 2010</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -919,6 +2323,26 @@
           <t>S72</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Finance Bill 2012, Memorandum explaining the provisions relating to direct taxes (Ministry of Finance)</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2012-2013/ub2012-13/mem/mem1.pdf</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>"Turnover or gross receipts for audit of accounts and presumptive taxation": the section 44AB limit for business goes from sixty lakh to one crore rupees, taking effect from 1 April 2013, assessment year 2013-14 (financial year 2012-13)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -926,6 +2350,26 @@
           <t>S73</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Finance Bill 2020, Memorandum explaining the provisions (Ministry of Finance), "Rationalisation of provisions relating to tax audit in certain cases"</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2020-21/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>the section 44AB limit for business goes from one crore to five crore rupees where cash receipts and cash payments in the year are each at most five per cent of the total; effective from 1 April 2020, assessment year 2020-21 (financial year 2019-20)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -933,6 +2377,26 @@
           <t>S74</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Finance Bill 2021, Memorandum explaining the provisions (Ministry of Finance), "Rationalisation of provisions relating to tax audit in certain cases"</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>https://www.indiabudget.gov.in/budget2021-22/doc/memo.pdf</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>the five crore limit goes to ten crore rupees on the same two cash conditions; effective from 1 April 2021, assessment year 2021-22 (financial year 2020-21)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -940,6 +2404,26 @@
           <t>S75</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Income-tax Act 1961, section 43(5) (speculative transaction), section 71 (set off of loss from one head against another) and section 72 (carry forward and set off of business losses), Indian Kanoon copies</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/967611/ ; https://indiankanoon.org/doc/178812545/ ; https://indiankanoon.org/doc/1004359/</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>43(5) first proviso (d), inserted from 1 April 2006: an eligible derivatives transaction on a recognised stock exchange is not speculative, so index futures give ordinary business income and loss; 71(2): a loss under another head may be set off against income under any head including capital gains; 72(1) and (3): a business loss not set off is carried forward to be set off against business profits only, for at most eight assessment years (the text carries no amendment note on the eight years)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -947,6 +2431,26 @@
           <t>S76</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Income-tax Act 2025, section 63 (tax audit) and section 112 (carry forward and set off of business loss), Indian Kanoon copies</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/167878245/ ; https://indiankanoon.org/doc/162039164/</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>from 1 April 2026 (tax year 2026-27): audit needed above one crore rupees of business turnover, ten crore where cash receipts and cash payments are each at most 5% (63(1) Table); business loss carried forward at most eight tax years and set off against business profits only (112(1), 112(2))</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -954,6 +2458,26 @@
           <t>S77</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ICAI Direct Taxes Committee, Guidance Note on Tax Audit under Section 44AB of the Income-tax Act 1961: Revised 2013 Edition (paragraph 5.12(b), pages 23 to 24) and 8th edition for assessment year 2022-23 (paragraph 5.14(b), page 17)</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>https://files2.pspcl.in/pdf/inst_fy_2014_15_revised_amended_audit_note.pdf ; https://www.caalley.com/icaipub/dt/71267dtc200822-gn44ab.pdf</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>turnover of derivatives, futures and options for the audit test: "the total of favourable and unfavourable differences shall be taken as turnover" (same words in both editions); each squared-off trade with a positive or negative difference counts on its own; sale value of the contract is not turnover</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -961,6 +2485,26 @@
           <t>S78</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tax audit fees quoted by service firms: FOAudit, Fees for F&amp;O Income Tax Audit; LegalAdda, Futures &amp; Options Tax Audit; TaxGarden, Tax Audit Fees by CA 2026</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>https://foaudit.com/fees-for-fo-income-tax-audit/ ; https://legaladda.com/future-options-fo-tax-audit/ ; https://taxgarden.in/blog/tax-audit-fees-by-ca-india-2026-cost-breakdown</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>no law or ICAI scale fixes the fee (TaxGarden: the ICAI scale is only recommended). F&amp;O specialists quote Rs 14,000 for tax audit, accounts and return together (FOAudit, LegalAdda); the general bands of TaxGarden for financial year 2025-26 are Rs 10,000 to 25,000 below Rs 1 crore of turnover and Rs 25,000 to 60,000 for Rs 1 crore to 5 crore. Asking prices of firms, not a survey</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -968,6 +2512,26 @@
           <t>S79</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Income-tax Act 1961, section 115BBDA (Indian Kanoon copy)</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>https://indiankanoon.org/doc/86116142/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>tax on dividends "declared, distributed or paid by a domestic company or companies" above Rs 10 lakh at ten per cent, on a resident individual, HUF or firm; the rest of the income is taxed as if the dividends were not there; no deduction or set-off of loss against the taxed dividend (115BBDA(2)), so income from units of a fund is outside it</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -980,7 +2544,7 @@
           <t>Finance Bill 2011, Memorandum explaining the provisions relating to direct taxes (Ministry of Finance)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>https://www.indiabudget.gov.in/budget2011-2012/ub2011-12/mem/mem1.pdf</t>
         </is>
@@ -998,7 +2562,86 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C82" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId2"/>
+    <hyperlink ref="C5" r:id="rId3"/>
+    <hyperlink ref="C6" r:id="rId4"/>
+    <hyperlink ref="C7" r:id="rId5"/>
+    <hyperlink ref="C8" r:id="rId6"/>
+    <hyperlink ref="C9" r:id="rId7"/>
+    <hyperlink ref="C10" r:id="rId8"/>
+    <hyperlink ref="C11" r:id="rId9"/>
+    <hyperlink ref="C12" r:id="rId10"/>
+    <hyperlink ref="C13" r:id="rId11"/>
+    <hyperlink ref="C14" r:id="rId12"/>
+    <hyperlink ref="C15" r:id="rId13"/>
+    <hyperlink ref="C16" r:id="rId14"/>
+    <hyperlink ref="C17" r:id="rId15"/>
+    <hyperlink ref="C18" r:id="rId16"/>
+    <hyperlink ref="C19" r:id="rId17"/>
+    <hyperlink ref="C20" r:id="rId18"/>
+    <hyperlink ref="C21" r:id="rId19"/>
+    <hyperlink ref="C22" r:id="rId20"/>
+    <hyperlink ref="C23" r:id="rId21"/>
+    <hyperlink ref="C24" r:id="rId22"/>
+    <hyperlink ref="C25" r:id="rId23"/>
+    <hyperlink ref="C26" r:id="rId24"/>
+    <hyperlink ref="C27" r:id="rId25"/>
+    <hyperlink ref="C28" r:id="rId26"/>
+    <hyperlink ref="C29" r:id="rId27"/>
+    <hyperlink ref="C30" r:id="rId28"/>
+    <hyperlink ref="C31" r:id="rId29"/>
+    <hyperlink ref="C32" r:id="rId30"/>
+    <hyperlink ref="C33" r:id="rId31"/>
+    <hyperlink ref="C34" r:id="rId32"/>
+    <hyperlink ref="C35" r:id="rId33"/>
+    <hyperlink ref="C36" r:id="rId34"/>
+    <hyperlink ref="C37" r:id="rId35"/>
+    <hyperlink ref="C38" r:id="rId36"/>
+    <hyperlink ref="C39" r:id="rId37"/>
+    <hyperlink ref="C40" r:id="rId38"/>
+    <hyperlink ref="C41" r:id="rId39"/>
+    <hyperlink ref="C42" r:id="rId40"/>
+    <hyperlink ref="C43" r:id="rId41"/>
+    <hyperlink ref="C44" r:id="rId42"/>
+    <hyperlink ref="C45" r:id="rId43"/>
+    <hyperlink ref="C46" r:id="rId44"/>
+    <hyperlink ref="C47" r:id="rId45"/>
+    <hyperlink ref="C48" r:id="rId46"/>
+    <hyperlink ref="C49" r:id="rId47"/>
+    <hyperlink ref="C50" r:id="rId48"/>
+    <hyperlink ref="C51" r:id="rId49"/>
+    <hyperlink ref="C52" r:id="rId50"/>
+    <hyperlink ref="C53" r:id="rId51"/>
+    <hyperlink ref="C54" r:id="rId52"/>
+    <hyperlink ref="C55" r:id="rId53"/>
+    <hyperlink ref="C56" r:id="rId54"/>
+    <hyperlink ref="C57" r:id="rId55"/>
+    <hyperlink ref="C58" r:id="rId56"/>
+    <hyperlink ref="C59" r:id="rId57"/>
+    <hyperlink ref="C60" r:id="rId58"/>
+    <hyperlink ref="C61" r:id="rId59"/>
+    <hyperlink ref="C62" r:id="rId60"/>
+    <hyperlink ref="C63" r:id="rId61"/>
+    <hyperlink ref="C64" r:id="rId62"/>
+    <hyperlink ref="C65" r:id="rId63"/>
+    <hyperlink ref="C66" r:id="rId64"/>
+    <hyperlink ref="C67" r:id="rId65"/>
+    <hyperlink ref="C68" r:id="rId66"/>
+    <hyperlink ref="C69" r:id="rId67"/>
+    <hyperlink ref="C70" r:id="rId68"/>
+    <hyperlink ref="C71" r:id="rId69"/>
+    <hyperlink ref="C72" r:id="rId70"/>
+    <hyperlink ref="C73" r:id="rId71"/>
+    <hyperlink ref="C74" r:id="rId72"/>
+    <hyperlink ref="C75" r:id="rId73"/>
+    <hyperlink ref="C76" r:id="rId74"/>
+    <hyperlink ref="C77" r:id="rId75"/>
+    <hyperlink ref="C78" r:id="rId76"/>
+    <hyperlink ref="C79" r:id="rId77"/>
+    <hyperlink ref="C80" r:id="rId78"/>
+    <hyperlink ref="C81" r:id="rId79"/>
+    <hyperlink ref="C82" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
